--- a/Bibsam_tidskriftslistor/scifree_data_acm.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_acm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_2B043A277E5AA59620393733AA874B555B69A73B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95DFCC8-6A1A-4AA6-BAAE-CEFB3DD87832}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B8FDAD-2202-4526-B0DB-EECBC7D9E35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="331">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -935,6 +935,84 @@
   </si>
   <si>
     <t>https://dl.acm.org/loi/eigrep</t>
+  </si>
+  <si>
+    <t>3068-8590</t>
+  </si>
+  <si>
+    <t>ACM AI Letters</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/ailet</t>
+  </si>
+  <si>
+    <t>3069-3497</t>
+  </si>
+  <si>
+    <t>ACM Journal of Data Science</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/acmjds</t>
+  </si>
+  <si>
+    <t>3066-4438</t>
+  </si>
+  <si>
+    <t>ACM Transactions on AI for Science</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/tais</t>
+  </si>
+  <si>
+    <t>3068-3564</t>
+  </si>
+  <si>
+    <t>ACM Transactions on AI Security and Privacy</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/taisap</t>
+  </si>
+  <si>
+    <t>1530-9312</t>
+  </si>
+  <si>
+    <t>0891-2017</t>
+  </si>
+  <si>
+    <t>Computational Linguistics</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/coli</t>
+  </si>
+  <si>
+    <t>1076-9757</t>
+  </si>
+  <si>
+    <t>Journal of Artificial Intelligence Research</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/jair</t>
+  </si>
+  <si>
+    <t>1931-3357</t>
+  </si>
+  <si>
+    <t>Journal of User Experience</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/jux</t>
+  </si>
+  <si>
+    <t>1533-7928</t>
+  </si>
+  <si>
+    <t>1532-4435</t>
+  </si>
+  <si>
+    <t>The Journal of Machine Learning Research</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/journal/jmlr</t>
   </si>
 </sst>
 </file>
@@ -990,19 +1068,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7E71E7E3-48AC-48E5-B6E2-9BF4D7766F23}" name="Table2" displayName="Table2" ref="A1:G81" totalsRowShown="0">
-  <autoFilter ref="A1:G81" xr:uid="{7E71E7E3-48AC-48E5-B6E2-9BF4D7766F23}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G81">
-    <sortCondition ref="D1:D81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{24572FE3-4A7A-4ED5-9023-CAE78ED6ED67}" name="Table1" displayName="Table1" ref="A1:G89" totalsRowShown="0">
+  <autoFilter ref="A1:G89" xr:uid="{24572FE3-4A7A-4ED5-9023-CAE78ED6ED67}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G89">
+    <sortCondition ref="D1:D89"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{17EE20B4-D8E6-4FA7-A90F-0F4002745591}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{31A6968F-4329-4B66-8ABB-42C2275EE9D5}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{CD1EEDCF-B32B-4F3A-AD12-462FFE64E7B3}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{655300E9-C230-44D0-9852-9F3F3D516969}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{39CE6508-4018-4EA5-AAF5-9BB53F9149CB}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{FA46763B-7845-4512-B0DA-E155E12F80D2}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{554C8457-1B69-4562-A7FD-4D53A264FCB4}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{DF3042EC-40A0-473D-9E2D-7D8B108AD08F}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{E14CC197-95B0-40EA-8D68-FB1E559B7389}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{B1B4B883-23E5-4643-AE53-C736FF066DF3}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{12362DAC-1F2A-47E9-9FAC-C3CFA29502FA}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{4C23D16E-BBD2-4BB5-BE5A-FA181298251D}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{0F651D5B-EB52-4457-A24B-577AF713CA75}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{E835B175-670D-4519-A58D-C54DDF29135D}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1270,14 +1348,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BA799D-7EAF-4CC7-9270-9B34940682D2}">
-  <dimension ref="A1:G81"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C855B44-6E6D-4F3F-9364-C1085B252A9C}">
+  <dimension ref="A1:G89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="62.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -1331,16 +1409,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G3" t="s">
         <v>7</v>
@@ -1351,19 +1429,16 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>120</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G4" t="s">
         <v>7</v>
@@ -1374,19 +1449,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>223</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G5" t="s">
         <v>7</v>
@@ -1397,16 +1472,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
@@ -1417,16 +1495,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="E7" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G7" t="s">
         <v>7</v>
@@ -1437,19 +1515,16 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>121</v>
+        <v>272</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>273</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -1460,16 +1535,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G9" t="s">
         <v>7</v>
@@ -1480,19 +1555,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -1503,19 +1578,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>123</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G11" t="s">
         <v>7</v>
@@ -1526,19 +1598,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G12" t="s">
         <v>7</v>
@@ -1549,16 +1621,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>125</v>
+        <v>311</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>313</v>
       </c>
       <c r="F13" t="s">
         <v>262</v>
@@ -1572,19 +1641,16 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>126</v>
+        <v>314</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>315</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>316</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G14" t="s">
         <v>7</v>
@@ -1595,19 +1661,19 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G15" t="s">
         <v>7</v>
@@ -1618,19 +1684,19 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G16" t="s">
         <v>7</v>
@@ -1641,19 +1707,19 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G17" t="s">
         <v>7</v>
@@ -1664,19 +1730,19 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G18" t="s">
         <v>7</v>
@@ -1687,19 +1753,19 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
@@ -1710,16 +1776,19 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G20" t="s">
         <v>7</v>
@@ -1730,19 +1799,19 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G21" t="s">
         <v>7</v>
@@ -1753,19 +1822,19 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G22" t="s">
         <v>7</v>
@@ -1776,19 +1845,19 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G23" t="s">
         <v>7</v>
@@ -1799,19 +1868,16 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G24" t="s">
         <v>7</v>
@@ -1822,19 +1888,19 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G25" t="s">
         <v>7</v>
@@ -1845,19 +1911,19 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G26" t="s">
         <v>7</v>
@@ -1868,19 +1934,19 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
@@ -1891,19 +1957,19 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G28" t="s">
         <v>7</v>
@@ -1914,13 +1980,16 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F29" t="s">
         <v>262</v>
@@ -1934,19 +2003,19 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
@@ -1957,19 +2026,19 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
@@ -1980,19 +2049,19 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G32" t="s">
         <v>7</v>
@@ -2003,19 +2072,16 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G33" t="s">
         <v>7</v>
@@ -2026,19 +2092,19 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
@@ -2049,19 +2115,19 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
@@ -2072,19 +2138,19 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G36" t="s">
         <v>7</v>
@@ -2095,19 +2161,19 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G37" t="s">
         <v>7</v>
@@ -2118,19 +2184,19 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G38" t="s">
         <v>7</v>
@@ -2141,19 +2207,19 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
@@ -2164,19 +2230,19 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G40" t="s">
         <v>7</v>
@@ -2187,19 +2253,19 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E41" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G41" t="s">
         <v>7</v>
@@ -2210,19 +2276,19 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G42" t="s">
         <v>7</v>
@@ -2233,13 +2299,16 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>281</v>
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>150</v>
       </c>
       <c r="D43" t="s">
-        <v>282</v>
+        <v>42</v>
       </c>
       <c r="E43" t="s">
-        <v>283</v>
+        <v>199</v>
       </c>
       <c r="F43" t="s">
         <v>262</v>
@@ -2253,19 +2322,19 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E44" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G44" t="s">
         <v>7</v>
@@ -2276,19 +2345,19 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G45" t="s">
         <v>7</v>
@@ -2299,16 +2368,19 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>284</v>
+        <v>100</v>
+      </c>
+      <c r="C46" t="s">
+        <v>153</v>
       </c>
       <c r="D46" t="s">
-        <v>285</v>
+        <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>286</v>
+        <v>202</v>
       </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G46" t="s">
         <v>7</v>
@@ -2319,19 +2391,16 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47" t="s">
-        <v>155</v>
+        <v>281</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>282</v>
       </c>
       <c r="E47" t="s">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="F47" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
@@ -2342,19 +2411,19 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G48" t="s">
         <v>7</v>
@@ -2365,19 +2434,19 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G49" t="s">
         <v>7</v>
@@ -2388,19 +2457,16 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50" t="s">
-        <v>158</v>
+        <v>284</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>285</v>
       </c>
       <c r="E50" t="s">
-        <v>207</v>
+        <v>286</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G50" t="s">
         <v>7</v>
@@ -2411,19 +2477,19 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E51" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G51" t="s">
         <v>7</v>
@@ -2434,19 +2500,19 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C52" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G52" t="s">
         <v>7</v>
@@ -2457,19 +2523,19 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G53" t="s">
         <v>7</v>
@@ -2480,16 +2546,19 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>105</v>
+      </c>
+      <c r="C54" t="s">
+        <v>158</v>
       </c>
       <c r="D54" t="s">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G54" t="s">
         <v>7</v>
@@ -2500,19 +2569,19 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="C55" t="s">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="F55" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G55" t="s">
         <v>7</v>
@@ -2523,16 +2592,16 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E56" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F56" t="s">
         <v>262</v>
@@ -2546,16 +2615,16 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C57" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F57" t="s">
         <v>262</v>
@@ -2569,16 +2638,16 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="D58" t="s">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="E58" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G58" t="s">
         <v>7</v>
@@ -2589,16 +2658,19 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>235</v>
+        <v>231</v>
+      </c>
+      <c r="C59" t="s">
+        <v>238</v>
       </c>
       <c r="D59" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E59" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G59" t="s">
         <v>7</v>
@@ -2609,19 +2681,19 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="C60" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="D60" t="s">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="E60" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="F60" t="s">
-        <v>262</v>
+        <v>8</v>
       </c>
       <c r="G60" t="s">
         <v>7</v>
@@ -2632,16 +2704,19 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>290</v>
+        <v>109</v>
+      </c>
+      <c r="C61" t="s">
+        <v>162</v>
       </c>
       <c r="D61" t="s">
-        <v>291</v>
+        <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>292</v>
+        <v>211</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G61" t="s">
         <v>7</v>
@@ -2652,19 +2727,19 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="C62" t="s">
-        <v>255</v>
+        <v>163</v>
       </c>
       <c r="D62" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="E62" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G62" t="s">
         <v>7</v>
@@ -2675,19 +2750,16 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>236</v>
-      </c>
-      <c r="C63" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="D63" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="E63" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
@@ -2698,19 +2770,16 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="D64" t="s">
-        <v>56</v>
+        <v>228</v>
       </c>
       <c r="E64" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
@@ -2721,19 +2790,19 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>264</v>
       </c>
       <c r="D65" t="s">
-        <v>57</v>
+        <v>265</v>
       </c>
       <c r="E65" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G65" t="s">
         <v>7</v>
@@ -2744,19 +2813,16 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
-      </c>
-      <c r="C66" t="s">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>291</v>
       </c>
       <c r="E66" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G66" t="s">
         <v>7</v>
@@ -2767,19 +2833,19 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
       <c r="C67" t="s">
-        <v>166</v>
+        <v>255</v>
       </c>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>251</v>
       </c>
       <c r="E67" t="s">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G67" t="s">
         <v>7</v>
@@ -2790,16 +2856,19 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>115</v>
+        <v>236</v>
+      </c>
+      <c r="C68" t="s">
+        <v>241</v>
       </c>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="F68" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G68" t="s">
         <v>7</v>
@@ -2809,14 +2878,14 @@
       <c r="A69" t="s">
         <v>9</v>
       </c>
-      <c r="B69" t="s">
-        <v>116</v>
+      <c r="C69" t="s">
+        <v>321</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>322</v>
       </c>
       <c r="E69" t="s">
-        <v>218</v>
+        <v>323</v>
       </c>
       <c r="F69" t="s">
         <v>8</v>
@@ -2830,16 +2899,19 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>111</v>
+      </c>
+      <c r="C70" t="s">
+        <v>164</v>
       </c>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E70" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F70" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G70" t="s">
         <v>7</v>
@@ -2850,13 +2922,16 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>293</v>
+        <v>112</v>
+      </c>
+      <c r="C71" t="s">
+        <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>294</v>
+        <v>57</v>
       </c>
       <c r="E71" t="s">
-        <v>295</v>
+        <v>214</v>
       </c>
       <c r="F71" t="s">
         <v>8</v>
@@ -2870,16 +2945,19 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>113</v>
+      </c>
+      <c r="C72" t="s">
+        <v>165</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E72" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F72" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G72" t="s">
         <v>7</v>
@@ -2889,14 +2967,14 @@
       <c r="A73" t="s">
         <v>9</v>
       </c>
-      <c r="B73" t="s">
-        <v>296</v>
+      <c r="C73" t="s">
+        <v>324</v>
       </c>
       <c r="D73" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="E73" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="F73" t="s">
         <v>8</v>
@@ -2910,13 +2988,16 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>119</v>
+        <v>114</v>
+      </c>
+      <c r="C74" t="s">
+        <v>166</v>
       </c>
       <c r="D74" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E74" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F74" t="s">
         <v>262</v>
@@ -2930,13 +3011,13 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>299</v>
+        <v>115</v>
       </c>
       <c r="D75" t="s">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="E75" t="s">
-        <v>301</v>
+        <v>217</v>
       </c>
       <c r="F75" t="s">
         <v>262</v>
@@ -2949,17 +3030,17 @@
       <c r="A76" t="s">
         <v>9</v>
       </c>
-      <c r="C76" t="s">
-        <v>260</v>
+      <c r="B76" t="s">
+        <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>259</v>
+        <v>61</v>
       </c>
       <c r="E76" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="F76" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
@@ -2970,19 +3051,16 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>232</v>
-      </c>
-      <c r="C77" t="s">
-        <v>239</v>
+        <v>117</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>62</v>
       </c>
       <c r="E77" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="F77" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
@@ -2993,16 +3071,16 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D78" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E78" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F78" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
@@ -3013,16 +3091,16 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="D79" t="s">
-        <v>249</v>
+        <v>63</v>
       </c>
       <c r="E79" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="F79" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G79" t="s">
         <v>7</v>
@@ -3033,16 +3111,16 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="D80" t="s">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="E80" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="F80" t="s">
-        <v>8</v>
+        <v>262</v>
       </c>
       <c r="G80" t="s">
         <v>7</v>
@@ -3053,21 +3131,187 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
+        <v>119</v>
+      </c>
+      <c r="D81" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" t="s">
+        <v>221</v>
+      </c>
+      <c r="F81" t="s">
+        <v>262</v>
+      </c>
+      <c r="G81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" t="s">
+        <v>299</v>
+      </c>
+      <c r="D82" t="s">
+        <v>300</v>
+      </c>
+      <c r="E82" t="s">
+        <v>301</v>
+      </c>
+      <c r="F82" t="s">
+        <v>262</v>
+      </c>
+      <c r="G82" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>260</v>
+      </c>
+      <c r="D83" t="s">
+        <v>259</v>
+      </c>
+      <c r="E83" t="s">
+        <v>261</v>
+      </c>
+      <c r="F83" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" t="s">
+        <v>232</v>
+      </c>
+      <c r="C84" t="s">
+        <v>239</v>
+      </c>
+      <c r="D84" t="s">
+        <v>225</v>
+      </c>
+      <c r="E84" t="s">
+        <v>244</v>
+      </c>
+      <c r="F84" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" t="s">
+        <v>302</v>
+      </c>
+      <c r="D85" t="s">
+        <v>303</v>
+      </c>
+      <c r="E85" t="s">
+        <v>304</v>
+      </c>
+      <c r="F85" t="s">
+        <v>262</v>
+      </c>
+      <c r="G85" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" t="s">
+        <v>252</v>
+      </c>
+      <c r="D86" t="s">
+        <v>249</v>
+      </c>
+      <c r="E86" t="s">
+        <v>256</v>
+      </c>
+      <c r="F86" t="s">
+        <v>262</v>
+      </c>
+      <c r="G86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" t="s">
+        <v>327</v>
+      </c>
+      <c r="C87" t="s">
+        <v>328</v>
+      </c>
+      <c r="D87" t="s">
+        <v>329</v>
+      </c>
+      <c r="E87" t="s">
+        <v>330</v>
+      </c>
+      <c r="F87" t="s">
+        <v>8</v>
+      </c>
+      <c r="G87" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" t="s">
+        <v>233</v>
+      </c>
+      <c r="D88" t="s">
+        <v>226</v>
+      </c>
+      <c r="E88" t="s">
+        <v>245</v>
+      </c>
+      <c r="F88" t="s">
+        <v>262</v>
+      </c>
+      <c r="G88" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" t="s">
         <v>234</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C89" t="s">
         <v>240</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D89" t="s">
         <v>227</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E89" t="s">
         <v>246</v>
       </c>
-      <c r="F81" t="s">
-        <v>8</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="F89" t="s">
+        <v>262</v>
+      </c>
+      <c r="G89" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Bibsam_tidskriftslistor/scifree_data_acm.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_acm.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B8FDAD-2202-4526-B0DB-EECBC7D9E35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E254D6C-31D8-4CCE-93AD-3A539FD0362A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="328">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -193,9 +193,6 @@
     <t>Journal of Data and Information Quality (JDIQ)</t>
   </si>
   <si>
-    <t>Journal of Experimental Algorithmics (JEA)</t>
-  </si>
-  <si>
     <t>Journal of the ACM (JACM)</t>
   </si>
   <si>
@@ -358,9 +355,6 @@
     <t>1936-1963</t>
   </si>
   <si>
-    <t>1084-6654</t>
-  </si>
-  <si>
     <t>1557-735X</t>
   </si>
   <si>
@@ -662,9 +656,6 @@
   </si>
   <si>
     <t>https://dl.acm.org/loi/jdiq</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/loi/jea</t>
   </si>
   <si>
     <t>https://dl.acm.org/loi/jacm</t>
@@ -1068,10 +1059,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{24572FE3-4A7A-4ED5-9023-CAE78ED6ED67}" name="Table1" displayName="Table1" ref="A1:G89" totalsRowShown="0">
-  <autoFilter ref="A1:G89" xr:uid="{24572FE3-4A7A-4ED5-9023-CAE78ED6ED67}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G89">
-    <sortCondition ref="D1:D89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{24572FE3-4A7A-4ED5-9023-CAE78ED6ED67}" name="Table1" displayName="Table1" ref="A1:G88" totalsRowShown="0">
+  <autoFilter ref="A1:G88" xr:uid="{24572FE3-4A7A-4ED5-9023-CAE78ED6ED67}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G88">
+    <sortCondition ref="D1:D88"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{DF3042EC-40A0-473D-9E2D-7D8B108AD08F}" name="Imprint"/>
@@ -1349,13 +1340,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C855B44-6E6D-4F3F-9364-C1085B252A9C}">
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -1389,16 +1380,16 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
@@ -1409,16 +1400,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G3" t="s">
         <v>7</v>
@@ -1429,16 +1420,16 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G4" t="s">
         <v>7</v>
@@ -1449,19 +1440,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G5" t="s">
         <v>7</v>
@@ -1472,19 +1463,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G6" t="s">
         <v>7</v>
@@ -1495,16 +1486,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G7" t="s">
         <v>7</v>
@@ -1515,16 +1506,16 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G8" t="s">
         <v>7</v>
@@ -1535,16 +1526,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G9" t="s">
         <v>7</v>
@@ -1555,19 +1546,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G10" t="s">
         <v>7</v>
@@ -1578,16 +1569,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G11" t="s">
         <v>7</v>
@@ -1598,19 +1589,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G12" t="s">
         <v>7</v>
@@ -1621,16 +1612,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G13" t="s">
         <v>7</v>
@@ -1641,16 +1632,16 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D14" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E14" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G14" t="s">
         <v>7</v>
@@ -1661,19 +1652,19 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G15" t="s">
         <v>7</v>
@@ -1684,19 +1675,19 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G16" t="s">
         <v>7</v>
@@ -1707,19 +1698,19 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F17" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G17" t="s">
         <v>7</v>
@@ -1730,19 +1721,19 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G18" t="s">
         <v>7</v>
@@ -1753,19 +1744,19 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
@@ -1776,19 +1767,19 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G20" t="s">
         <v>7</v>
@@ -1799,19 +1790,19 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G21" t="s">
         <v>7</v>
@@ -1822,19 +1813,19 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F22" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G22" t="s">
         <v>7</v>
@@ -1845,19 +1836,19 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
       </c>
       <c r="E23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F23" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G23" t="s">
         <v>7</v>
@@ -1868,16 +1859,16 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F24" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G24" t="s">
         <v>7</v>
@@ -1888,19 +1879,19 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F25" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G25" t="s">
         <v>7</v>
@@ -1911,19 +1902,19 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F26" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G26" t="s">
         <v>7</v>
@@ -1934,19 +1925,19 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
@@ -1957,19 +1948,19 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F28" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G28" t="s">
         <v>7</v>
@@ -1980,19 +1971,19 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F29" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
@@ -2003,19 +1994,19 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s">
         <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
@@ -2026,19 +2017,19 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s">
         <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
@@ -2049,19 +2040,19 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
         <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G32" t="s">
         <v>7</v>
@@ -2072,16 +2063,16 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
         <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G33" t="s">
         <v>7</v>
@@ -2092,19 +2083,19 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
@@ -2115,19 +2106,19 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
         <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
@@ -2138,19 +2129,19 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D36" t="s">
         <v>34</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G36" t="s">
         <v>7</v>
@@ -2161,19 +2152,19 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D37" t="s">
         <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G37" t="s">
         <v>7</v>
@@ -2184,19 +2175,19 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D38" t="s">
         <v>37</v>
       </c>
       <c r="E38" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F38" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G38" t="s">
         <v>7</v>
@@ -2207,19 +2198,19 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
         <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F39" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
@@ -2230,19 +2221,19 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F40" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G40" t="s">
         <v>7</v>
@@ -2253,19 +2244,19 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
         <v>40</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F41" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G41" t="s">
         <v>7</v>
@@ -2276,19 +2267,19 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D42" t="s">
         <v>41</v>
       </c>
       <c r="E42" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F42" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G42" t="s">
         <v>7</v>
@@ -2299,19 +2290,19 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>42</v>
       </c>
       <c r="E43" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F43" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G43" t="s">
         <v>7</v>
@@ -2322,19 +2313,19 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
         <v>43</v>
       </c>
       <c r="E44" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F44" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G44" t="s">
         <v>7</v>
@@ -2345,19 +2336,19 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D45" t="s">
         <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F45" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G45" t="s">
         <v>7</v>
@@ -2368,19 +2359,19 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
         <v>45</v>
       </c>
       <c r="E46" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F46" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G46" t="s">
         <v>7</v>
@@ -2391,16 +2382,16 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E47" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F47" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
@@ -2411,19 +2402,19 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F48" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G48" t="s">
         <v>7</v>
@@ -2434,19 +2425,19 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F49" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G49" t="s">
         <v>7</v>
@@ -2457,16 +2448,16 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D50" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E50" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F50" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G50" t="s">
         <v>7</v>
@@ -2477,19 +2468,19 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D51" t="s">
         <v>47</v>
       </c>
       <c r="E51" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F51" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G51" t="s">
         <v>7</v>
@@ -2500,19 +2491,19 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C52" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D52" t="s">
         <v>48</v>
       </c>
       <c r="E52" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F52" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G52" t="s">
         <v>7</v>
@@ -2523,19 +2514,19 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G53" t="s">
         <v>7</v>
@@ -2546,19 +2537,19 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D54" t="s">
         <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F54" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G54" t="s">
         <v>7</v>
@@ -2569,19 +2560,19 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
         <v>51</v>
       </c>
       <c r="E55" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F55" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G55" t="s">
         <v>7</v>
@@ -2592,19 +2583,19 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D56" t="s">
         <v>52</v>
       </c>
       <c r="E56" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G56" t="s">
         <v>7</v>
@@ -2615,19 +2606,19 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D57" t="s">
         <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F57" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G57" t="s">
         <v>7</v>
@@ -2638,16 +2629,16 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D58" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E58" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F58" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G58" t="s">
         <v>7</v>
@@ -2658,19 +2649,19 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C59" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D59" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E59" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F59" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G59" t="s">
         <v>7</v>
@@ -2681,16 +2672,16 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
+        <v>314</v>
+      </c>
+      <c r="C60" t="s">
+        <v>315</v>
+      </c>
+      <c r="D60" t="s">
+        <v>316</v>
+      </c>
+      <c r="E60" t="s">
         <v>317</v>
-      </c>
-      <c r="C60" t="s">
-        <v>318</v>
-      </c>
-      <c r="D60" t="s">
-        <v>319</v>
-      </c>
-      <c r="E60" t="s">
-        <v>320</v>
       </c>
       <c r="F60" t="s">
         <v>8</v>
@@ -2704,19 +2695,19 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D61" t="s">
         <v>54</v>
       </c>
       <c r="E61" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F61" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G61" t="s">
         <v>7</v>
@@ -2727,19 +2718,19 @@
         <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C62" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D62" t="s">
         <v>55</v>
       </c>
       <c r="E62" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G62" t="s">
         <v>7</v>
@@ -2750,16 +2741,16 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D63" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E63" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F63" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
@@ -2770,16 +2761,16 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D64" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E64" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
@@ -2790,19 +2781,19 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C65" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E65" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F65" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G65" t="s">
         <v>7</v>
@@ -2813,16 +2804,16 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D66" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E66" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F66" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G66" t="s">
         <v>7</v>
@@ -2833,19 +2824,19 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s">
+        <v>252</v>
+      </c>
+      <c r="D67" t="s">
+        <v>248</v>
+      </c>
+      <c r="E67" t="s">
         <v>255</v>
       </c>
-      <c r="D67" t="s">
-        <v>251</v>
-      </c>
-      <c r="E67" t="s">
-        <v>258</v>
-      </c>
       <c r="F67" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G67" t="s">
         <v>7</v>
@@ -2856,19 +2847,19 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C68" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D68" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E68" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F68" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G68" t="s">
         <v>7</v>
@@ -2879,13 +2870,13 @@
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D69" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E69" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F69" t="s">
         <v>8</v>
@@ -2899,19 +2890,19 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C70" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D70" t="s">
         <v>56</v>
       </c>
       <c r="E70" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F70" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G70" t="s">
         <v>7</v>
@@ -2922,19 +2913,19 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D71" t="s">
         <v>57</v>
       </c>
       <c r="E71" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F71" t="s">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="G71" t="s">
         <v>7</v>
@@ -2944,20 +2935,17 @@
       <c r="A72" t="s">
         <v>9</v>
       </c>
-      <c r="B72" t="s">
-        <v>113</v>
-      </c>
       <c r="C72" t="s">
-        <v>165</v>
+        <v>321</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>322</v>
       </c>
       <c r="E72" t="s">
-        <v>215</v>
+        <v>323</v>
       </c>
       <c r="F72" t="s">
-        <v>262</v>
+        <v>8</v>
       </c>
       <c r="G72" t="s">
         <v>7</v>
@@ -2967,17 +2955,20 @@
       <c r="A73" t="s">
         <v>9</v>
       </c>
+      <c r="B73" t="s">
+        <v>112</v>
+      </c>
       <c r="C73" t="s">
-        <v>324</v>
+        <v>164</v>
       </c>
       <c r="D73" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="E73" t="s">
-        <v>326</v>
+        <v>213</v>
       </c>
       <c r="F73" t="s">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="G73" t="s">
         <v>7</v>
@@ -2988,19 +2979,16 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>114</v>
-      </c>
-      <c r="C74" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="D74" t="s">
         <v>59</v>
       </c>
       <c r="E74" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F74" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G74" t="s">
         <v>7</v>
@@ -3011,16 +2999,16 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
         <v>60</v>
       </c>
       <c r="E75" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G75" t="s">
         <v>7</v>
@@ -3031,16 +3019,16 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D76" t="s">
         <v>61</v>
       </c>
       <c r="E76" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F76" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
@@ -3051,16 +3039,16 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>290</v>
       </c>
       <c r="D77" t="s">
-        <v>62</v>
+        <v>291</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
+        <v>292</v>
       </c>
       <c r="F77" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
@@ -3071,16 +3059,16 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>293</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
-        <v>294</v>
+        <v>62</v>
       </c>
       <c r="E78" t="s">
-        <v>295</v>
+        <v>217</v>
       </c>
       <c r="F78" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
@@ -3091,16 +3079,16 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>118</v>
+        <v>293</v>
       </c>
       <c r="D79" t="s">
-        <v>63</v>
+        <v>294</v>
       </c>
       <c r="E79" t="s">
-        <v>220</v>
+        <v>295</v>
       </c>
       <c r="F79" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G79" t="s">
         <v>7</v>
@@ -3111,16 +3099,16 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>296</v>
+        <v>117</v>
       </c>
       <c r="D80" t="s">
-        <v>297</v>
+        <v>63</v>
       </c>
       <c r="E80" t="s">
-        <v>298</v>
+        <v>218</v>
       </c>
       <c r="F80" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G80" t="s">
         <v>7</v>
@@ -3131,16 +3119,16 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>119</v>
+        <v>296</v>
       </c>
       <c r="D81" t="s">
-        <v>64</v>
+        <v>297</v>
       </c>
       <c r="E81" t="s">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="F81" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
@@ -3150,17 +3138,17 @@
       <c r="A82" t="s">
         <v>9</v>
       </c>
-      <c r="B82" t="s">
-        <v>299</v>
+      <c r="C82" t="s">
+        <v>257</v>
       </c>
       <c r="D82" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="E82" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
       <c r="F82" t="s">
-        <v>262</v>
+        <v>8</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -3170,14 +3158,17 @@
       <c r="A83" t="s">
         <v>9</v>
       </c>
+      <c r="B83" t="s">
+        <v>229</v>
+      </c>
       <c r="C83" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="D83" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="E83" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="F83" t="s">
         <v>8</v>
@@ -3191,19 +3182,16 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>232</v>
-      </c>
-      <c r="C84" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
       <c r="D84" t="s">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="E84" t="s">
-        <v>244</v>
+        <v>301</v>
       </c>
       <c r="F84" t="s">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="G84" t="s">
         <v>7</v>
@@ -3214,16 +3202,16 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="D85" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="E85" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="F85" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G85" t="s">
         <v>7</v>
@@ -3234,16 +3222,19 @@
         <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>252</v>
+        <v>324</v>
+      </c>
+      <c r="C86" t="s">
+        <v>325</v>
       </c>
       <c r="D86" t="s">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="E86" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="F86" t="s">
-        <v>262</v>
+        <v>8</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -3254,19 +3245,16 @@
         <v>9</v>
       </c>
       <c r="B87" t="s">
-        <v>327</v>
-      </c>
-      <c r="C87" t="s">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="D87" t="s">
-        <v>329</v>
+        <v>223</v>
       </c>
       <c r="E87" t="s">
-        <v>330</v>
+        <v>242</v>
       </c>
       <c r="F87" t="s">
-        <v>8</v>
+        <v>259</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -3277,41 +3265,21 @@
         <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>231</v>
+      </c>
+      <c r="C88" t="s">
+        <v>237</v>
       </c>
       <c r="D88" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E88" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G88" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89" t="s">
-        <v>234</v>
-      </c>
-      <c r="C89" t="s">
-        <v>240</v>
-      </c>
-      <c r="D89" t="s">
-        <v>227</v>
-      </c>
-      <c r="E89" t="s">
-        <v>246</v>
-      </c>
-      <c r="F89" t="s">
-        <v>262</v>
-      </c>
-      <c r="G89" t="s">
         <v>7</v>
       </c>
     </row>
